--- a/exports/trend_1d/HINDZINC_full_report.xlsx
+++ b/exports/trend_1d/HINDZINC_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q89"/>
+  <dimension ref="A1:U89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>8.01</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42083</v>
+        <v>42086</v>
       </c>
       <c r="H2" t="n">
-        <v>164.75</v>
+        <v>162.94</v>
       </c>
       <c r="I2" t="n">
         <v>163.7560532264176</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K2" t="n">
-        <v>7.05</v>
+        <v>5.87</v>
       </c>
       <c r="L2" t="n">
         <v>0.88</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>11.44</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42128</v>
+        <v>42129</v>
       </c>
       <c r="H3" t="n">
-        <v>172.35</v>
+        <v>182.35</v>
       </c>
       <c r="I3" t="n">
         <v>177.7723954261684</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.78</v>
+        <v>-11.91</v>
       </c>
       <c r="L3" t="n">
-        <v>7.4</v>
+        <v>12.59</v>
       </c>
       <c r="M3" t="n">
         <v>1.59</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>12.32</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42187</v>
+        <v>42188</v>
       </c>
       <c r="H4" t="n">
-        <v>164.15</v>
+        <v>161.65</v>
       </c>
       <c r="I4" t="n">
         <v>163.0272779651436</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K4" t="n">
-        <v>-9.98</v>
+        <v>-11.35</v>
       </c>
       <c r="L4" t="n">
-        <v>10.89</v>
+        <v>11.68</v>
       </c>
       <c r="M4" t="n">
         <v>1.33</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>8.35</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42270</v>
+        <v>42271</v>
       </c>
       <c r="H5" t="n">
-        <v>135.4</v>
+        <v>143.25</v>
       </c>
       <c r="I5" t="n">
         <v>143.2106479608165</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K5" t="n">
-        <v>16.24</v>
+        <v>11.38</v>
       </c>
       <c r="L5" t="n">
         <v>5.41</v>
@@ -726,7 +785,7 @@
         <v>2.89</v>
       </c>
       <c r="N5" t="n">
-        <v>4.53</v>
+        <v>5.8</v>
       </c>
       <c r="O5" t="n">
         <v>-1.52</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>15.93</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42325</v>
+        <v>42326</v>
       </c>
       <c r="H6" t="n">
-        <v>147.55</v>
+        <v>140.9</v>
       </c>
       <c r="I6" t="n">
         <v>142.0923158072114</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>-1.64</v>
       </c>
       <c r="L6" t="n">
         <v>6.39</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>13.75</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42394</v>
+        <v>42396</v>
       </c>
       <c r="H7" t="n">
-        <v>151.19</v>
+        <v>159.75</v>
       </c>
       <c r="I7" t="n">
         <v>151.3647894880384</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.3</v>
+        <v>-13.38</v>
       </c>
       <c r="L7" t="n">
-        <v>8.59</v>
+        <v>16.04</v>
       </c>
       <c r="M7" t="n">
         <v>1.59</v>
       </c>
       <c r="N7" t="n">
-        <v>4.31</v>
+        <v>5.66</v>
       </c>
       <c r="O7" t="n">
         <v>-4.51</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>12.77</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42465</v>
+        <v>42466</v>
       </c>
       <c r="H8" t="n">
-        <v>186.75</v>
+        <v>162.19</v>
       </c>
       <c r="I8" t="n">
         <v>170.078439011787</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K8" t="n">
-        <v>16.9</v>
+        <v>1.53</v>
       </c>
       <c r="L8" t="n">
         <v>5.51</v>
       </c>
       <c r="M8" t="n">
-        <v>1.61</v>
+        <v>12.72</v>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>13.15</v>
       </c>
       <c r="O8" t="n">
         <v>5.66</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>14.93</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42550</v>
+        <v>42551</v>
       </c>
       <c r="H9" t="n">
-        <v>177.05</v>
+        <v>180.55</v>
       </c>
       <c r="I9" t="n">
         <v>177.2105524097508</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K9" t="n">
-        <v>-9.16</v>
+        <v>-11.32</v>
       </c>
       <c r="L9" t="n">
-        <v>11.1</v>
+        <v>11.91</v>
       </c>
       <c r="M9" t="n">
         <v>1.92</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,25 +1109,25 @@
         <v>8.5</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42622</v>
+        <v>42625</v>
       </c>
       <c r="H10" t="n">
-        <v>220.35</v>
+        <v>212.55</v>
       </c>
       <c r="I10" t="n">
         <v>212.582298883757</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K10" t="n">
-        <v>22.04</v>
+        <v>17.72</v>
       </c>
       <c r="L10" t="n">
         <v>2.46</v>
       </c>
       <c r="M10" t="n">
-        <v>2.98</v>
+        <v>3.56</v>
       </c>
       <c r="N10" t="n">
         <v>3.62</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>10.2</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42643</v>
+        <v>42646</v>
       </c>
       <c r="H11" t="n">
-        <v>233.35</v>
+        <v>254.45</v>
       </c>
       <c r="I11" t="n">
         <v>234.229828702367</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K11" t="n">
-        <v>-9.789999999999999</v>
+        <v>-19.71</v>
       </c>
       <c r="L11" t="n">
-        <v>11.22</v>
+        <v>23.5</v>
       </c>
       <c r="M11" t="n">
         <v>1.89</v>
       </c>
       <c r="N11" t="n">
-        <v>3.67</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="O11" t="n">
         <v>-3.54</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>13.37</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42685</v>
+        <v>42689</v>
       </c>
       <c r="H12" t="n">
-        <v>249.75</v>
+        <v>238.6</v>
       </c>
       <c r="I12" t="n">
         <v>242.7924649095501</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.85</v>
+        <v>-6.23</v>
       </c>
       <c r="L12" t="n">
         <v>13.15</v>
@@ -1125,7 +1268,7 @@
         <v>9.970000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>4.32</v>
+        <v>4.46</v>
       </c>
       <c r="O12" t="n">
         <v>9.039999999999999</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>20.61</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42699</v>
+        <v>42702</v>
       </c>
       <c r="H13" t="n">
-        <v>273.25</v>
+        <v>284.5</v>
       </c>
       <c r="I13" t="n">
         <v>282.0611070622018</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K13" t="n">
-        <v>-14.52</v>
+        <v>-19.24</v>
       </c>
       <c r="L13" t="n">
-        <v>17.93</v>
+        <v>20.28</v>
       </c>
       <c r="M13" t="n">
         <v>3.04</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>15.15</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42727</v>
+        <v>42730</v>
       </c>
       <c r="H14" t="n">
-        <v>258.45</v>
+        <v>249.7</v>
       </c>
       <c r="I14" t="n">
         <v>256.3131262809686</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K14" t="n">
-        <v>-9.16</v>
+        <v>-12.23</v>
       </c>
       <c r="L14" t="n">
-        <v>10.47</v>
+        <v>12.65</v>
       </c>
       <c r="M14" t="n">
         <v>1.51</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>12.21</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42745</v>
+        <v>42746</v>
       </c>
       <c r="H15" t="n">
-        <v>272.85</v>
+        <v>278.14</v>
       </c>
       <c r="I15" t="n">
         <v>277.3023212150042</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K15" t="n">
-        <v>-9.27</v>
+        <v>-11.39</v>
       </c>
       <c r="L15" t="n">
-        <v>9.970000000000001</v>
+        <v>12.29</v>
       </c>
       <c r="M15" t="n">
         <v>2.07</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42780</v>
+        <v>42781</v>
       </c>
       <c r="H16" t="n">
-        <v>303.39</v>
+        <v>293.14</v>
       </c>
       <c r="I16" t="n">
         <v>295.3846203390569</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K16" t="n">
-        <v>9.08</v>
+        <v>5.39</v>
       </c>
       <c r="L16" t="n">
         <v>2.5</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>13.12</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42816</v>
+        <v>42817</v>
       </c>
       <c r="H17" t="n">
-        <v>311.85</v>
+        <v>319.55</v>
       </c>
       <c r="I17" t="n">
         <v>316.5029384635734</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.38</v>
+        <v>-9.01</v>
       </c>
       <c r="L17" t="n">
-        <v>9.08</v>
+        <v>9.85</v>
       </c>
       <c r="M17" t="n">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="N17" t="n">
         <v>5.27</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42822</v>
+        <v>42823</v>
       </c>
       <c r="H18" t="n">
-        <v>326</v>
+        <v>290.05</v>
       </c>
       <c r="I18" t="n">
         <v>296.6397938157661</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K18" t="n">
-        <v>2.02</v>
+        <v>-9.23</v>
       </c>
       <c r="L18" t="n">
-        <v>0.99</v>
+        <v>9.44</v>
       </c>
       <c r="M18" t="n">
-        <v>0.03</v>
+        <v>9.59</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>11.03</v>
       </c>
       <c r="O18" t="n">
         <v>2.47</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>12.94</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42905</v>
+        <v>42906</v>
       </c>
       <c r="H19" t="n">
-        <v>246.6</v>
+        <v>253.2</v>
       </c>
       <c r="I19" t="n">
         <v>252.9710626595974</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K19" t="n">
-        <v>14.98</v>
+        <v>12.7</v>
       </c>
       <c r="L19" t="n">
         <v>1.62</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>9.16</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43053</v>
+        <v>43054</v>
       </c>
       <c r="H20" t="n">
-        <v>309.89</v>
+        <v>296.39</v>
       </c>
       <c r="I20" t="n">
         <v>300.334770011298</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K20" t="n">
-        <v>22.39</v>
+        <v>17.06</v>
       </c>
       <c r="L20" t="n">
         <v>3.63</v>
@@ -1581,7 +1820,7 @@
         <v>1.22</v>
       </c>
       <c r="N20" t="n">
-        <v>3.67</v>
+        <v>4.36</v>
       </c>
       <c r="O20" t="n">
         <v>2.68</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>6</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>10.08</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43090</v>
+        <v>43091</v>
       </c>
       <c r="H21" t="n">
-        <v>303.45</v>
+        <v>307.7</v>
       </c>
       <c r="I21" t="n">
         <v>307.1728928039075</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.38</v>
+        <v>-3.82</v>
       </c>
       <c r="L21" t="n">
         <v>8.130000000000001</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,25 +1937,25 @@
         <v>7.16</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43118</v>
+        <v>43119</v>
       </c>
       <c r="H22" t="n">
-        <v>308.3</v>
+        <v>299.35</v>
       </c>
       <c r="I22" t="n">
         <v>306.1509522032868</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K22" t="n">
-        <v>0.19</v>
+        <v>-2.71</v>
       </c>
       <c r="L22" t="n">
-        <v>2.19</v>
+        <v>3.25</v>
       </c>
       <c r="M22" t="n">
-        <v>-0</v>
+        <v>0.39</v>
       </c>
       <c r="N22" t="n">
         <v>4.59</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>10.34</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43153</v>
+        <v>43154</v>
       </c>
       <c r="H23" t="n">
-        <v>314.14</v>
+        <v>328</v>
       </c>
       <c r="I23" t="n">
         <v>317.6508329181178</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.94</v>
+        <v>-9.57</v>
       </c>
       <c r="L23" t="n">
-        <v>6.65</v>
+        <v>9.9</v>
       </c>
       <c r="M23" t="n">
         <v>2.26</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>11.48</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43181</v>
+        <v>43182</v>
       </c>
       <c r="H24" t="n">
-        <v>312.75</v>
+        <v>301.45</v>
       </c>
       <c r="I24" t="n">
         <v>303.6272344646666</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.65</v>
+        <v>-8.09</v>
       </c>
       <c r="L24" t="n">
-        <v>7.91</v>
+        <v>9.65</v>
       </c>
       <c r="M24" t="n">
-        <v>1.72</v>
+        <v>4.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.32</v>
+        <v>3.61</v>
       </c>
       <c r="O24" t="n">
         <v>4.41</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43335</v>
+        <v>43336</v>
       </c>
       <c r="H25" t="n">
-        <v>286.2</v>
+        <v>292.3</v>
       </c>
       <c r="I25" t="n">
         <v>289.0267526847392</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K25" t="n">
-        <v>5.06</v>
+        <v>3.04</v>
       </c>
       <c r="L25" t="n">
         <v>11.63</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>6</v>
+      </c>
+      <c r="U25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>8.68</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43378</v>
+        <v>43381</v>
       </c>
       <c r="H26" t="n">
-        <v>280.89</v>
+        <v>270.64</v>
       </c>
       <c r="I26" t="n">
         <v>278.4060644784891</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.9</v>
+        <v>-7.41</v>
       </c>
       <c r="L26" t="n">
-        <v>7.99</v>
+        <v>9.68</v>
       </c>
       <c r="M26" t="n">
         <v>0.85</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>14.49</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43452</v>
+        <v>43453</v>
       </c>
       <c r="H27" t="n">
-        <v>277.8</v>
+        <v>282.3</v>
       </c>
       <c r="I27" t="n">
         <v>281.1086219089898</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.65</v>
+        <v>-4.31</v>
       </c>
       <c r="L27" t="n">
         <v>8.960000000000001</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>8.1</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43487</v>
+        <v>43488</v>
       </c>
       <c r="H28" t="n">
-        <v>260.25</v>
+        <v>259.39</v>
       </c>
       <c r="I28" t="n">
         <v>259.4447339914246</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K28" t="n">
-        <v>-7.81</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="L28" t="n">
         <v>9.19</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>6.79</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43523</v>
+        <v>43524</v>
       </c>
       <c r="H29" t="n">
-        <v>263.89</v>
+        <v>269.45</v>
       </c>
       <c r="I29" t="n">
         <v>266.4299104833331</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.73</v>
+        <v>-3.88</v>
       </c>
       <c r="L29" t="n">
-        <v>3.7</v>
+        <v>5.01</v>
       </c>
       <c r="M29" t="n">
         <v>0.9399999999999999</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>8.49</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43591</v>
+        <v>43592</v>
       </c>
       <c r="H30" t="n">
-        <v>272.55</v>
+        <v>268.05</v>
       </c>
       <c r="I30" t="n">
         <v>268.2420570019257</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K30" t="n">
-        <v>1.15</v>
+        <v>-0.52</v>
       </c>
       <c r="L30" t="n">
         <v>2.93</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43642</v>
+        <v>43643</v>
       </c>
       <c r="H31" t="n">
-        <v>240.9</v>
+        <v>244.6</v>
       </c>
       <c r="I31" t="n">
         <v>243.6108928879836</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K31" t="n">
-        <v>10.13</v>
+        <v>8.75</v>
       </c>
       <c r="L31" t="n">
         <v>2.57</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>7.94</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43655</v>
+        <v>43656</v>
       </c>
       <c r="H32" t="n">
-        <v>230.45</v>
+        <v>223.1</v>
       </c>
       <c r="I32" t="n">
         <v>228.077350676194</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K32" t="n">
-        <v>-5.78</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>7.6</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M32" t="n">
         <v>0.49</v>
       </c>
       <c r="N32" t="n">
-        <v>2.3</v>
+        <v>3.19</v>
       </c>
       <c r="O32" t="n">
         <v>1.54</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>10</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43721</v>
+        <v>43724</v>
       </c>
       <c r="H33" t="n">
-        <v>217.8</v>
+        <v>219.65</v>
       </c>
       <c r="I33" t="n">
         <v>218.5436587542478</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K33" t="n">
-        <v>2.38</v>
+        <v>1.55</v>
       </c>
       <c r="L33" t="n">
         <v>3.99</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>9.09</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43854</v>
+        <v>43857</v>
       </c>
       <c r="H34" t="n">
-        <v>207.85</v>
+        <v>201</v>
       </c>
       <c r="I34" t="n">
         <v>203.8511874414189</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K34" t="n">
-        <v>-5.37</v>
+        <v>-8.49</v>
       </c>
       <c r="L34" t="n">
         <v>10.2</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43924</v>
+        <v>43928</v>
       </c>
       <c r="H35" t="n">
-        <v>161.55</v>
+        <v>164.5</v>
       </c>
       <c r="I35" t="n">
         <v>163.1833801019414</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K35" t="n">
-        <v>19.63</v>
+        <v>18.16</v>
       </c>
       <c r="L35" t="n">
         <v>3.53</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>22.45</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43972</v>
+        <v>43973</v>
       </c>
       <c r="H36" t="n">
-        <v>169.3</v>
+        <v>165.25</v>
       </c>
       <c r="I36" t="n">
         <v>166.4364509142691</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K36" t="n">
-        <v>2.92</v>
+        <v>0.46</v>
       </c>
       <c r="L36" t="n">
         <v>2.95</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>16.78</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44006</v>
+        <v>44007</v>
       </c>
       <c r="H37" t="n">
-        <v>186.95</v>
+        <v>189.65</v>
       </c>
       <c r="I37" t="n">
         <v>188.0244636346858</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K37" t="n">
-        <v>-13.13</v>
+        <v>-14.77</v>
       </c>
       <c r="L37" t="n">
         <v>18.03</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>11.9</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44081</v>
+        <v>44082</v>
       </c>
       <c r="H38" t="n">
-        <v>217.8</v>
+        <v>211.9</v>
       </c>
       <c r="I38" t="n">
         <v>214.7053081026045</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K38" t="n">
-        <v>14.84</v>
+        <v>11.73</v>
       </c>
       <c r="L38" t="n">
         <v>3.9</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,25 +3110,25 @@
         <v>12.6</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44124</v>
+        <v>44125</v>
       </c>
       <c r="H39" t="n">
-        <v>222.85</v>
+        <v>233.1</v>
       </c>
       <c r="I39" t="n">
         <v>229.8906312451624</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.17</v>
+        <v>-10</v>
       </c>
       <c r="L39" t="n">
         <v>12.79</v>
       </c>
       <c r="M39" t="n">
-        <v>2.89</v>
+        <v>3.99</v>
       </c>
       <c r="N39" t="n">
         <v>7.44</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>13.59</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44131</v>
+        <v>44132</v>
       </c>
       <c r="H40" t="n">
-        <v>214.7</v>
+        <v>210.25</v>
       </c>
       <c r="I40" t="n">
         <v>213.0359535317555</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K40" t="n">
-        <v>-7.89</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>9.33</v>
+        <v>10.32</v>
       </c>
       <c r="M40" t="n">
         <v>9.550000000000001</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>15.74</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44161</v>
+        <v>44162</v>
       </c>
       <c r="H41" t="n">
-        <v>221</v>
+        <v>229.7</v>
       </c>
       <c r="I41" t="n">
         <v>229.4799106941304</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.11</v>
+        <v>-9.25</v>
       </c>
       <c r="L41" t="n">
-        <v>9.390000000000001</v>
+        <v>12.06</v>
       </c>
       <c r="M41" t="n">
         <v>1.3</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>10.11</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44221</v>
+        <v>44223</v>
       </c>
       <c r="H42" t="n">
-        <v>268.05</v>
+        <v>264</v>
       </c>
       <c r="I42" t="n">
         <v>267.3724192793445</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K42" t="n">
-        <v>16.7</v>
+        <v>14.93</v>
       </c>
       <c r="L42" t="n">
         <v>3.66</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>18.31</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44256</v>
+        <v>44257</v>
       </c>
       <c r="H43" t="n">
-        <v>300.15</v>
+        <v>315.3</v>
       </c>
       <c r="I43" t="n">
         <v>307.6084965891903</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K43" t="n">
-        <v>-13.69</v>
+        <v>-19.43</v>
       </c>
       <c r="L43" t="n">
-        <v>18.18</v>
+        <v>22.31</v>
       </c>
       <c r="M43" t="n">
         <v>5.55</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>12.3</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44273</v>
+        <v>44274</v>
       </c>
       <c r="H44" t="n">
-        <v>286.35</v>
+        <v>283.35</v>
       </c>
       <c r="I44" t="n">
         <v>283.8891554610623</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K44" t="n">
-        <v>-9.18</v>
+        <v>-10.13</v>
       </c>
       <c r="L44" t="n">
-        <v>10.21</v>
+        <v>13.64</v>
       </c>
       <c r="M44" t="n">
         <v>1.18</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,25 +3524,25 @@
         <v>13.49</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44292</v>
+        <v>44293</v>
       </c>
       <c r="H45" t="n">
-        <v>301.35</v>
+        <v>307.5</v>
       </c>
       <c r="I45" t="n">
         <v>304.1180933446503</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.35</v>
+        <v>-8.52</v>
       </c>
       <c r="L45" t="n">
-        <v>9.050000000000001</v>
+        <v>12.05</v>
       </c>
       <c r="M45" t="n">
-        <v>1.93</v>
+        <v>3.53</v>
       </c>
       <c r="N45" t="n">
         <v>6.07</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>14.15</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44403</v>
+        <v>44404</v>
       </c>
       <c r="H46" t="n">
-        <v>326.5</v>
+        <v>320.45</v>
       </c>
       <c r="I46" t="n">
         <v>322.0266585273629</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K46" t="n">
-        <v>6.18</v>
+        <v>4.21</v>
       </c>
       <c r="L46" t="n">
         <v>9.380000000000001</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,25 +3662,25 @@
         <v>10.14</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44482</v>
+        <v>44483</v>
       </c>
       <c r="H47" t="n">
-        <v>332.85</v>
+        <v>346.7</v>
       </c>
       <c r="I47" t="n">
         <v>333.7147479493601</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.87</v>
+        <v>-8.19</v>
       </c>
       <c r="L47" t="n">
-        <v>6.41</v>
+        <v>12.65</v>
       </c>
       <c r="M47" t="n">
-        <v>1.29</v>
+        <v>5.15</v>
       </c>
       <c r="N47" t="n">
         <v>4.42</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>6.92</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44489</v>
+        <v>44490</v>
       </c>
       <c r="H48" t="n">
-        <v>359.9</v>
+        <v>342.05</v>
       </c>
       <c r="I48" t="n">
         <v>342.2181036489471</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K48" t="n">
-        <v>3.81</v>
+        <v>-1.34</v>
       </c>
       <c r="L48" t="n">
-        <v>0.49</v>
+        <v>1.93</v>
       </c>
       <c r="M48" t="n">
         <v>0.08</v>
       </c>
       <c r="N48" t="n">
-        <v>4.73</v>
+        <v>4.96</v>
       </c>
       <c r="O48" t="n">
         <v>4.16</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>19.54</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44532</v>
+        <v>44533</v>
       </c>
       <c r="H49" t="n">
-        <v>333.3</v>
+        <v>347.65</v>
       </c>
       <c r="I49" t="n">
         <v>346.9899636244249</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K49" t="n">
-        <v>2.56</v>
+        <v>-1.64</v>
       </c>
       <c r="L49" t="n">
         <v>8.08</v>
       </c>
       <c r="M49" t="n">
-        <v>2.27</v>
+        <v>3.54</v>
       </c>
       <c r="N49" t="n">
-        <v>2.48</v>
+        <v>4.31</v>
       </c>
       <c r="O49" t="n">
         <v>-4.96</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>9.42</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44543</v>
+        <v>44544</v>
       </c>
       <c r="H50" t="n">
-        <v>367.95</v>
+        <v>338.6</v>
       </c>
       <c r="I50" t="n">
         <v>341.8880924312316</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K50" t="n">
-        <v>5.84</v>
+        <v>-2.6</v>
       </c>
       <c r="L50" t="n">
-        <v>2.19</v>
+        <v>4.17</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="N50" t="n">
-        <v>0.48</v>
+        <v>7.98</v>
       </c>
       <c r="O50" t="n">
         <v>4.31</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>10.97</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44620</v>
+        <v>44622</v>
       </c>
       <c r="H51" t="n">
-        <v>311.95</v>
+        <v>351.75</v>
       </c>
       <c r="I51" t="n">
         <v>328.8917236217914</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K51" t="n">
-        <v>7.87</v>
+        <v>-3.88</v>
       </c>
       <c r="L51" t="n">
-        <v>3.97</v>
+        <v>6.32</v>
       </c>
       <c r="M51" t="n">
         <v>3.79</v>
       </c>
       <c r="N51" t="n">
-        <v>3.9</v>
+        <v>12.76</v>
       </c>
       <c r="O51" t="n">
         <v>-7.98</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>16.72</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44673</v>
+        <v>44676</v>
       </c>
       <c r="H52" t="n">
-        <v>345.35</v>
+        <v>322.85</v>
       </c>
       <c r="I52" t="n">
         <v>323.0606104637405</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.82</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="L52" t="n">
         <v>13.29</v>
       </c>
       <c r="M52" t="n">
-        <v>0.26</v>
+        <v>0.83</v>
       </c>
       <c r="N52" t="n">
-        <v>5.61</v>
+        <v>6.52</v>
       </c>
       <c r="O52" t="n">
         <v>12.76</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>13.33</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44750</v>
+        <v>44753</v>
       </c>
       <c r="H53" t="n">
-        <v>263.05</v>
+        <v>271.4</v>
       </c>
       <c r="I53" t="n">
         <v>271.388819486334</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K53" t="n">
-        <v>18.52</v>
+        <v>15.94</v>
       </c>
       <c r="L53" t="n">
         <v>6.09</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>11.36</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44767</v>
+        <v>44768</v>
       </c>
       <c r="H54" t="n">
-        <v>273.05</v>
+        <v>265.9</v>
       </c>
       <c r="I54" t="n">
         <v>271.0337558696468</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K54" t="n">
-        <v>0.61</v>
+        <v>-2.03</v>
       </c>
       <c r="L54" t="n">
         <v>3.08</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>11.68</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44785</v>
+        <v>44789</v>
       </c>
       <c r="H55" t="n">
-        <v>273.7</v>
+        <v>293.2</v>
       </c>
       <c r="I55" t="n">
         <v>289.4856735218791</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.93</v>
+        <v>-10.27</v>
       </c>
       <c r="L55" t="n">
-        <v>4.29</v>
+        <v>13.58</v>
       </c>
       <c r="M55" t="n">
         <v>1.4</v>
       </c>
       <c r="N55" t="n">
-        <v>1.97</v>
+        <v>7.12</v>
       </c>
       <c r="O55" t="n">
         <v>-2.62</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>10.81</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H56" t="n">
-        <v>278.4</v>
+        <v>272.45</v>
       </c>
       <c r="I56" t="n">
         <v>273.4745648095621</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K56" t="n">
-        <v>-5.05</v>
+        <v>-7.08</v>
       </c>
       <c r="L56" t="n">
-        <v>7.4</v>
+        <v>8.25</v>
       </c>
       <c r="M56" t="n">
         <v>1.84</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>7.47</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44840</v>
+        <v>44841</v>
       </c>
       <c r="H57" t="n">
-        <v>284.55</v>
+        <v>287.8</v>
       </c>
       <c r="I57" t="n">
         <v>286.0509747793017</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.44</v>
+        <v>-5.63</v>
       </c>
       <c r="L57" t="n">
-        <v>4.72</v>
+        <v>5.85</v>
       </c>
       <c r="M57" t="n">
         <v>3.36</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44887</v>
+        <v>44888</v>
       </c>
       <c r="H58" t="n">
-        <v>319.55</v>
+        <v>301.05</v>
       </c>
       <c r="I58" t="n">
         <v>306.0477681020199</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K58" t="n">
-        <v>11.03</v>
+        <v>4.6</v>
       </c>
       <c r="L58" t="n">
         <v>4.1</v>
       </c>
       <c r="M58" t="n">
-        <v>0.97</v>
+        <v>4.83</v>
       </c>
       <c r="N58" t="n">
-        <v>2.89</v>
+        <v>5.79</v>
       </c>
       <c r="O58" t="n">
         <v>1.14</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>7.86</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44902</v>
+        <v>44903</v>
       </c>
       <c r="H59" t="n">
-        <v>315.05</v>
+        <v>317.2</v>
       </c>
       <c r="I59" t="n">
         <v>316.9201099134382</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K59" t="n">
-        <v>-4.65</v>
+        <v>-5.36</v>
       </c>
       <c r="L59" t="n">
         <v>5.93</v>
       </c>
       <c r="M59" t="n">
-        <v>0.51</v>
+        <v>0.62</v>
       </c>
       <c r="N59" t="n">
         <v>2.83</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>6.21</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>44953</v>
+        <v>44956</v>
       </c>
       <c r="H60" t="n">
-        <v>346.35</v>
+        <v>330</v>
       </c>
       <c r="I60" t="n">
         <v>342.1585825562792</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K60" t="n">
-        <v>9.19</v>
+        <v>4.04</v>
       </c>
       <c r="L60" t="n">
         <v>3.22</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>12.9</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45009</v>
+        <v>45012</v>
       </c>
       <c r="H61" t="n">
-        <v>323.1</v>
+        <v>329.1</v>
       </c>
       <c r="I61" t="n">
         <v>325.5929644530499</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K61" t="n">
-        <v>2.09</v>
+        <v>0.27</v>
       </c>
       <c r="L61" t="n">
         <v>5.94</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>8.779999999999999</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45013</v>
+        <v>45014</v>
       </c>
       <c r="H62" t="n">
-        <v>328.8</v>
+        <v>299</v>
       </c>
       <c r="I62" t="n">
         <v>300.9550803448234</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.09</v>
+        <v>-9.15</v>
       </c>
       <c r="L62" t="n">
-        <v>1.76</v>
+        <v>10.36</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>9.06</v>
       </c>
       <c r="N62" t="n">
-        <v>0.09</v>
+        <v>9.06</v>
       </c>
       <c r="O62" t="n">
         <v>1.86</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,25 +4766,25 @@
         <v>11.34</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45035</v>
+        <v>45036</v>
       </c>
       <c r="H63" t="n">
-        <v>324.45</v>
+        <v>327.55</v>
       </c>
       <c r="I63" t="n">
         <v>327.1089714286238</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K63" t="n">
-        <v>-8.51</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>9.029999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="M63" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="N63" t="n">
         <v>2.52</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>6.58</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45070</v>
+        <v>45071</v>
       </c>
       <c r="H64" t="n">
-        <v>306.55</v>
+        <v>304.9</v>
       </c>
       <c r="I64" t="n">
         <v>306.0044852085845</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K64" t="n">
-        <v>-6.41</v>
+        <v>-6.91</v>
       </c>
       <c r="L64" t="n">
-        <v>6.55</v>
+        <v>7.07</v>
       </c>
       <c r="M64" t="n">
         <v>1.42</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>4.11</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45111</v>
+        <v>45112</v>
       </c>
       <c r="H65" t="n">
-        <v>310.75</v>
+        <v>311.5</v>
       </c>
       <c r="I65" t="n">
         <v>311.154454272247</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K65" t="n">
-        <v>-1.92</v>
+        <v>-2.16</v>
       </c>
       <c r="L65" t="n">
         <v>2.85</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>3.4</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45124</v>
+        <v>45125</v>
       </c>
       <c r="H66" t="n">
-        <v>323.95</v>
+        <v>320.3</v>
       </c>
       <c r="I66" t="n">
         <v>322.5616842305699</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K66" t="n">
-        <v>4</v>
+        <v>2.83</v>
       </c>
       <c r="L66" t="n">
         <v>0.32</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>6.44</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45212</v>
+        <v>45215</v>
       </c>
       <c r="H67" t="n">
-        <v>318.6</v>
+        <v>321.9</v>
       </c>
       <c r="I67" t="n">
         <v>320.0612664762959</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K67" t="n">
-        <v>0.53</v>
+        <v>-0.5</v>
       </c>
       <c r="L67" t="n">
         <v>2.4</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>4</v>
+      </c>
+      <c r="U67" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>6.56</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45222</v>
+        <v>45224</v>
       </c>
       <c r="H68" t="n">
-        <v>303.45</v>
+        <v>299.7</v>
       </c>
       <c r="I68" t="n">
         <v>302.5841972212333</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K68" t="n">
-        <v>-5.73</v>
+        <v>-6.9</v>
       </c>
       <c r="L68" t="n">
-        <v>6.71</v>
+        <v>7.86</v>
       </c>
       <c r="M68" t="n">
         <v>1.04</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>9.02</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45261</v>
+        <v>45264</v>
       </c>
       <c r="H69" t="n">
-        <v>300.15</v>
+        <v>317.9</v>
       </c>
       <c r="I69" t="n">
         <v>313.2618485472331</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.15</v>
+        <v>-6.07</v>
       </c>
       <c r="L69" t="n">
-        <v>3.09</v>
+        <v>6.44</v>
       </c>
       <c r="M69" t="n">
-        <v>1.23</v>
+        <v>6.25</v>
       </c>
       <c r="N69" t="n">
-        <v>1.75</v>
+        <v>5.91</v>
       </c>
       <c r="O69" t="n">
         <v>-1.24</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>6.32</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45279</v>
+        <v>45280</v>
       </c>
       <c r="H70" t="n">
-        <v>311.95</v>
+        <v>306.9</v>
       </c>
       <c r="I70" t="n">
         <v>309.2124636681604</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K70" t="n">
-        <v>-1.87</v>
+        <v>-3.46</v>
       </c>
       <c r="L70" t="n">
-        <v>2.33</v>
+        <v>3.82</v>
       </c>
       <c r="M70" t="n">
         <v>0.35</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>6.56</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="H71" t="n">
-        <v>306.15</v>
+        <v>315.65</v>
       </c>
       <c r="I71" t="n">
         <v>310.6063068019642</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K71" t="n">
-        <v>0.24</v>
+        <v>-2.85</v>
       </c>
       <c r="L71" t="n">
         <v>6.04</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>5</v>
+      </c>
+      <c r="U71" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45497</v>
+        <v>45498</v>
       </c>
       <c r="H72" t="n">
-        <v>634.35</v>
+        <v>611.45</v>
       </c>
       <c r="I72" t="n">
         <v>617.3510574524245</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K72" t="n">
-        <v>100.97</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="L72" t="n">
         <v>3.58</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>4</v>
+      </c>
+      <c r="U72" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>12.89</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45588</v>
+        <v>45589</v>
       </c>
       <c r="H73" t="n">
-        <v>523.7</v>
+        <v>539.5</v>
       </c>
       <c r="I73" t="n">
         <v>528.0229113894923</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K73" t="n">
-        <v>14.35</v>
+        <v>11.77</v>
       </c>
       <c r="L73" t="n">
         <v>8.460000000000001</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>10.36</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45608</v>
+        <v>45609</v>
       </c>
       <c r="H74" t="n">
-        <v>500.7</v>
+        <v>485.7</v>
       </c>
       <c r="I74" t="n">
         <v>500.6821731428098</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K74" t="n">
-        <v>-7.19</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>8.43</v>
+        <v>10.29</v>
       </c>
       <c r="M74" t="n">
         <v>7.08</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>14</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45678</v>
+        <v>45679</v>
       </c>
       <c r="H75" t="n">
-        <v>461</v>
+        <v>469.35</v>
       </c>
       <c r="I75" t="n">
         <v>468.6117603805952</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K75" t="n">
-        <v>5.09</v>
+        <v>3.37</v>
       </c>
       <c r="L75" t="n">
         <v>6.32</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4752,22 +5663,22 @@
         <v>9.779999999999999</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45698</v>
+        <v>45699</v>
       </c>
       <c r="H76" t="n">
-        <v>435.65</v>
+        <v>416.85</v>
       </c>
       <c r="I76" t="n">
         <v>430.3065479965266</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K76" t="n">
-        <v>-7.18</v>
+        <v>-11.19</v>
       </c>
       <c r="L76" t="n">
-        <v>9.119999999999999</v>
+        <v>11.8</v>
       </c>
       <c r="M76" t="n">
         <v>1.04</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,22 +5732,22 @@
         <v>14.78</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45729</v>
+        <v>45733</v>
       </c>
       <c r="H77" t="n">
-        <v>430</v>
+        <v>435.35</v>
       </c>
       <c r="I77" t="n">
         <v>431.345560987989</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K77" t="n">
-        <v>-3.15</v>
+        <v>-4.44</v>
       </c>
       <c r="L77" t="n">
-        <v>5.18</v>
+        <v>6.03</v>
       </c>
       <c r="M77" t="n">
         <v>1.64</v>
@@ -4839,7 +5762,19 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,25 +5801,25 @@
         <v>8.75</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H78" t="n">
-        <v>426.95</v>
+        <v>406.75</v>
       </c>
       <c r="I78" t="n">
         <v>416.4288219872172</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K78" t="n">
-        <v>-1.93</v>
+        <v>-6.57</v>
       </c>
       <c r="L78" t="n">
-        <v>2.61</v>
+        <v>10.75</v>
       </c>
       <c r="M78" t="n">
-        <v>0.64</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="N78" t="n">
         <v>7.01</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>12.77</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>45770</v>
+        <v>45771</v>
       </c>
       <c r="H79" t="n">
-        <v>449.05</v>
+        <v>459.35</v>
       </c>
       <c r="I79" t="n">
         <v>458.7028961547682</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K79" t="n">
-        <v>-10.4</v>
+        <v>-12.93</v>
       </c>
       <c r="L79" t="n">
-        <v>13.28</v>
+        <v>14.22</v>
       </c>
       <c r="M79" t="n">
         <v>3.59</v>
@@ -4953,7 +5900,19 @@
         <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S79" t="b">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4980,28 +5939,28 @@
         <v>12.27</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>45825</v>
+        <v>45826</v>
       </c>
       <c r="H80" t="n">
-        <v>486.35</v>
+        <v>452.8</v>
       </c>
       <c r="I80" t="n">
         <v>484.3293645320799</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K80" t="n">
-        <v>5.88</v>
+        <v>-1.43</v>
       </c>
       <c r="L80" t="n">
         <v>13.36</v>
       </c>
       <c r="M80" t="n">
-        <v>2.77</v>
+        <v>5.01</v>
       </c>
       <c r="N80" t="n">
-        <v>5.19</v>
+        <v>6.9</v>
       </c>
       <c r="O80" t="n">
         <v>2.29</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +6008,19 @@
         <v>14.97</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>45902</v>
+        <v>45903</v>
       </c>
       <c r="H81" t="n">
-        <v>440.9</v>
+        <v>444.6</v>
       </c>
       <c r="I81" t="n">
         <v>443.9644691975116</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K81" t="n">
-        <v>2.63</v>
+        <v>1.81</v>
       </c>
       <c r="L81" t="n">
         <v>2.69</v>
@@ -5067,7 +6038,19 @@
         <v>1</v>
       </c>
       <c r="Q81" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>4</v>
+      </c>
+      <c r="U81" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -5094,25 +6077,25 @@
         <v>6.3</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="H82" t="n">
-        <v>472.15</v>
+        <v>458.3</v>
       </c>
       <c r="I82" t="n">
         <v>466.7430340486131</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K82" t="n">
-        <v>6.2</v>
+        <v>3.08</v>
       </c>
       <c r="L82" t="n">
         <v>3.12</v>
       </c>
       <c r="M82" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="N82" t="n">
         <v>3.78</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>3</v>
+      </c>
+      <c r="U82" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -5151,28 +6146,28 @@
         <v>8.84</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="H83" t="n">
-        <v>485.2</v>
+        <v>499.85</v>
       </c>
       <c r="I83" t="n">
         <v>490.8759269549371</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K83" t="n">
-        <v>-5.87</v>
+        <v>-9.07</v>
       </c>
       <c r="L83" t="n">
-        <v>6.74</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M83" t="n">
-        <v>1.2</v>
+        <v>3.07</v>
       </c>
       <c r="N83" t="n">
-        <v>2.24</v>
+        <v>3.02</v>
       </c>
       <c r="O83" t="n">
         <v>-2.93</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -5208,28 +6215,28 @@
         <v>7.34</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="H84" t="n">
-        <v>715.2</v>
+        <v>628.5</v>
       </c>
       <c r="I84" t="n">
         <v>634.8870516022685</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K84" t="n">
-        <v>43.08</v>
+        <v>25.74</v>
       </c>
       <c r="L84" t="n">
         <v>3.57</v>
       </c>
       <c r="M84" t="n">
-        <v>2.09</v>
+        <v>3.52</v>
       </c>
       <c r="N84" t="n">
-        <v>6.23</v>
+        <v>12.12</v>
       </c>
       <c r="O84" t="n">
         <v>3.02</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>3</v>
+      </c>
+      <c r="U84" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -5265,19 +6284,19 @@
         <v>21.17</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H85" t="n">
-        <v>538.75</v>
+        <v>559.35</v>
       </c>
       <c r="I85" t="n">
         <v>558.8706248211265</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K85" t="n">
-        <v>14.28</v>
+        <v>11</v>
       </c>
       <c r="L85" t="n">
         <v>9.789999999999999</v>
@@ -5295,7 +6314,19 @@
         <v>1</v>
       </c>
       <c r="Q85" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>3</v>
+      </c>
+      <c r="U85" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -5322,19 +6353,19 @@
         <v>11.54</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H86" t="n">
-        <v>610.55</v>
+        <v>603.85</v>
       </c>
       <c r="I86" t="n">
         <v>610.195698183485</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K86" t="n">
-        <v>9.15</v>
+        <v>7.96</v>
       </c>
       <c r="L86" t="n">
         <v>2.22</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S86" t="b">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>3</v>
+      </c>
+      <c r="U86" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -5379,19 +6422,19 @@
         <v>9.34</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="H87" t="n">
-        <v>547</v>
+        <v>562.9</v>
       </c>
       <c r="I87" t="n">
         <v>555.5159888211067</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K87" t="n">
-        <v>9.41</v>
+        <v>6.78</v>
       </c>
       <c r="L87" t="n">
         <v>1.56</v>
@@ -5400,7 +6443,7 @@
         <v>2.93</v>
       </c>
       <c r="N87" t="n">
-        <v>2.73</v>
+        <v>2.91</v>
       </c>
       <c r="O87" t="n">
         <v>-1.1</v>
@@ -5409,7 +6452,19 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S87" t="b">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>3</v>
+      </c>
+      <c r="U87" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -5436,19 +6491,19 @@
         <v>7.83</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H88" t="n">
-        <v>576.45</v>
+        <v>560.9</v>
       </c>
       <c r="I88" t="n">
         <v>561.3389303534819</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K88" t="n">
-        <v>2.41</v>
+        <v>-0.36</v>
       </c>
       <c r="L88" t="n">
         <v>2.9</v>
@@ -5466,7 +6521,19 @@
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R88" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S88" t="b">
+        <v>1</v>
+      </c>
+      <c r="T88" t="n">
+        <v>2</v>
+      </c>
+      <c r="U88" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -5517,6 +6584,14 @@
       <c r="Q89" t="n">
         <v>30</v>
       </c>
+      <c r="R89" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S89" t="b">
+        <v>1</v>
+      </c>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10475,7 +11550,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47.4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -10485,7 +11560,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -10495,7 +11570,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8">
@@ -10505,7 +11580,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -10515,7 +11590,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67.5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -10525,7 +11600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>82.8</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="11">
@@ -10535,7 +11610,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -10545,7 +11620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -10555,7 +11630,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33.3</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="14">
@@ -10565,7 +11640,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.37</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="15">
@@ -10575,7 +11650,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.09</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="16">
@@ -10585,7 +11660,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.4</v>
+        <v>-3.62</v>
       </c>
     </row>
     <row r="17">
@@ -10595,7 +11670,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>100.97</v>
+        <v>93.70999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -10605,7 +11680,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48.3</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="19">
@@ -10615,7 +11690,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.51</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="20">
@@ -10625,7 +11700,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.09</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="21">
@@ -10635,7 +11710,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.18</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="22">
@@ -10645,7 +11720,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23">
@@ -10655,7 +11730,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
@@ -10665,7 +11740,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.34</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="25">
@@ -10675,7 +11750,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9.970000000000001</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="26">
@@ -10685,7 +11760,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.37</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="27">
@@ -10695,7 +11770,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.31</v>
+        <v>13.15</v>
       </c>
     </row>
     <row r="28">
@@ -10705,7 +11780,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29">
